--- a/InputData/ccs/CC/CCS Calculations.xlsx
+++ b/InputData/ccs/CC/CCS Calculations.xlsx
@@ -4778,4 +4778,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95583942-FA47-4F16-B942-6BBAB1CEABC1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62828CFF-5610-4370-9BD0-A1526FD0A911}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{808E7C5F-F96E-4C88-B602-2E3A0BDDE059}"/>
 </file>
--- a/InputData/ccs/CC/CCS Calculations.xlsx
+++ b/InputData/ccs/CC/CCS Calculations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\ccs\CC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\SouthKorea EPS\InputData\ccs\CC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAC8057-3D10-459B-A73B-36B6485E5AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A07097E-3EAF-452E-AEBA-7F6D5642025A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2604" yWindow="348" windowWidth="17076" windowHeight="12828" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -749,59 +749,59 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.26953125" customWidth="1"/>
-    <col min="2" max="2" width="55.81640625" customWidth="1"/>
-    <col min="4" max="4" width="30.54296875" customWidth="1"/>
+    <col min="1" max="1" width="30.21875" customWidth="1"/>
+    <col min="2" max="2" width="55.77734375" customWidth="1"/>
+    <col min="4" max="4" width="30.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -809,70 +809,70 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>0.88711067149387013</v>
       </c>
@@ -880,7 +880,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3412141</v>
       </c>
@@ -900,14 +900,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.7265625" customWidth="1"/>
-    <col min="2" max="2" width="42.54296875" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.77734375" customWidth="1"/>
+    <col min="2" max="2" width="42.5546875" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>95</v>
       </c>
@@ -942,7 +942,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -1879,13 +1879,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.7265625" customWidth="1"/>
-    <col min="2" max="2" width="42.54296875" customWidth="1"/>
+    <col min="1" max="1" width="26.77734375" customWidth="1"/>
+    <col min="2" max="2" width="42.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>95</v>
       </c>
@@ -1899,7 +1899,7 @@
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>6.1418537999999999E-7</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>86</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>87</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>8.7009595499999985E-6</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>88</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>89</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>90</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>91</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>92</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>93</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>94</v>
       </c>
@@ -1990,18 +1990,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA25B772-A559-4F07-971A-AC3B6FFE9BE6}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="34.77734375" customWidth="1"/>
     <col min="2" max="9" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>259016</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>91.77</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -2204,12 +2204,12 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>Industrial Furnace</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>259016</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>152.94</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -2460,12 +2460,12 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" t="s">
         <v>31</v>
@@ -2483,7 +2483,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B23" t="str">
         <f>B3</f>
         <v>Natural Gas Processing</v>
@@ -2517,7 +2517,7 @@
         <v>Industrial Furnace</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>48</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>571.58457392593505</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>545942.56000000006</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>8871566.5999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -2665,12 +2665,12 @@
         <v>22.863382957037402</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>97</v>
       </c>
@@ -2686,18 +2686,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.453125" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="1" max="1" width="44.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>442.08384092059458</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -2933,18 +2933,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.453125" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="1" max="1" width="44.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>80.122912914199276</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>214.0302346757544</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>157.60743456534033</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>85.494272870387022</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3180,18 +3180,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.453125" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="1" max="1" width="44.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -3200,76 +3200,76 @@
         <v>210.77627576977025</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" s="3"/>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" s="3"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="3"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" s="3"/>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" s="3"/>
     </row>
   </sheetData>
@@ -3283,18 +3283,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.1796875" customWidth="1"/>
-    <col min="2" max="2" width="25.81640625" customWidth="1"/>
+    <col min="1" max="1" width="19.21875" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -3321,7 +3321,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3357,7 +3357,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>17.683353636823785</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -3456,7 +3456,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -3483,7 +3483,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3530,18 +3530,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.1796875" customWidth="1"/>
-    <col min="2" max="2" width="25.81640625" customWidth="1"/>
+    <col min="1" max="1" width="19.21875" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>5.6086039039939504</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>14.98211642730281</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>7.8803717282670158</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>5.1296563722232209</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3777,18 +3777,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.1796875" customWidth="1"/>
-    <col min="2" max="2" width="25.81640625" customWidth="1"/>
+    <col min="1" max="1" width="19.21875" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -3808,14 +3808,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46.81640625" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.77734375" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>95</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -4220,7 +4220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -4781,6 +4781,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -4924,15 +4933,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -4940,13 +4940,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95583942-FA47-4F16-B942-6BBAB1CEABC1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62828CFF-5610-4370-9BD0-A1526FD0A911}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62828CFF-5610-4370-9BD0-A1526FD0A911}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95583942-FA47-4F16-B942-6BBAB1CEABC1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{808E7C5F-F96E-4C88-B602-2E3A0BDDE059}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{808E7C5F-F96E-4C88-B602-2E3A0BDDE059}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>